--- a/src/main/resources/in/Outstation Weekly Income Statements Jan to Dec 14.xlsx
+++ b/src/main/resources/in/Outstation Weekly Income Statements Jan to Dec 14.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Church\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kiari\IdeaProjects\income_statement_generator\src\main\resources\in\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB451B84-7373-459F-9714-28017D2621EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41F4BAE6-A8B2-4A0D-91E9-35DB0AE7B47A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" firstSheet="2" activeTab="3" xr2:uid="{D15CB871-78DB-4C2D-9746-E8E83178CF8B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="2" activeTab="2" xr2:uid="{D15CB871-78DB-4C2D-9746-E8E83178CF8B}"/>
   </bookViews>
   <sheets>
     <sheet name="2024 INCOME STATEMENT (PARTLY)" sheetId="2" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="40">
   <si>
     <t>Date</t>
   </si>
@@ -153,6 +153,12 @@
   </si>
   <si>
     <t>ADN Festival Celebratory Lunch Contribution</t>
+  </si>
+  <si>
+    <t>Githiga Joint Mass Lunch</t>
+  </si>
+  <si>
+    <t>Gatitu Joint Mass Stipend</t>
   </si>
 </sst>
 </file>
@@ -196,11 +202,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -542,29 +547,29 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{512F4729-CA0B-48EE-BDCC-3DFB94189E32}">
   <dimension ref="A1:E24"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.453125" customWidth="1"/>
+    <col min="3" max="3" width="7.42578125" customWidth="1"/>
     <col min="4" max="4" width="11" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.81640625" customWidth="1"/>
+    <col min="5" max="5" width="8.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4" t="s">
+      <c r="C1" s="3"/>
+      <c r="D1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="4"/>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="E1" s="3"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>5</v>
       </c>
@@ -578,7 +583,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>45508</v>
       </c>
@@ -595,7 +600,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>45515</v>
       </c>
@@ -612,7 +617,7 @@
         <v>925</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>45522</v>
       </c>
@@ -629,7 +634,7 @@
         <v>925</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>45529</v>
       </c>
@@ -646,7 +651,7 @@
         <v>925</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>45536</v>
       </c>
@@ -663,7 +668,7 @@
         <v>1015</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>45543</v>
       </c>
@@ -680,7 +685,7 @@
         <v>925</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>45550</v>
       </c>
@@ -697,7 +702,7 @@
         <v>925</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>45557</v>
       </c>
@@ -714,7 +719,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>45564</v>
       </c>
@@ -731,7 +736,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>45571</v>
       </c>
@@ -748,7 +753,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>45578</v>
       </c>
@@ -765,7 +770,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>45585</v>
       </c>
@@ -782,7 +787,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>45592</v>
       </c>
@@ -799,7 +804,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>45599</v>
       </c>
@@ -816,7 +821,7 @@
         <v>945</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>45606</v>
       </c>
@@ -833,7 +838,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>45613</v>
       </c>
@@ -850,7 +855,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>45985</v>
       </c>
@@ -867,7 +872,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>45992</v>
       </c>
@@ -884,7 +889,7 @@
         <v>895</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>45999</v>
       </c>
@@ -901,7 +906,7 @@
         <v>895</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>46006</v>
       </c>
@@ -918,7 +923,7 @@
         <v>1415</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>46013</v>
       </c>
@@ -935,7 +940,7 @@
         <v>895</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>46020</v>
       </c>
@@ -964,12 +969,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{707241FC-1CA3-4592-B37E-D59A72CF8500}">
   <dimension ref="A1:H25"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="39.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="39.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -983,7 +988,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>45535</v>
       </c>
@@ -994,7 +999,7 @@
         <v>820</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>45556</v>
       </c>
@@ -1005,7 +1010,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>45557</v>
       </c>
@@ -1016,7 +1021,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>45557</v>
       </c>
@@ -1027,7 +1032,7 @@
         <v>820</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>45570</v>
       </c>
@@ -1038,7 +1043,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>45578</v>
       </c>
@@ -1049,7 +1054,7 @@
         <v>2550</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>45585</v>
       </c>
@@ -1061,7 +1066,7 @@
       </c>
       <c r="H8" s="1"/>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>45596</v>
       </c>
@@ -1073,7 +1078,7 @@
       </c>
       <c r="H9" s="1"/>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>45596</v>
       </c>
@@ -1085,7 +1090,7 @@
       </c>
       <c r="H10" s="1"/>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>45964</v>
       </c>
@@ -1097,7 +1102,7 @@
       </c>
       <c r="H11" s="1"/>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>45971</v>
       </c>
@@ -1109,7 +1114,7 @@
       </c>
       <c r="H12" s="1"/>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>45978</v>
       </c>
@@ -1121,7 +1126,7 @@
       </c>
       <c r="H13" s="1"/>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>45985</v>
       </c>
@@ -1133,7 +1138,7 @@
       </c>
       <c r="H14" s="1"/>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>45992</v>
       </c>
@@ -1145,7 +1150,7 @@
       </c>
       <c r="H15" s="1"/>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>45992</v>
       </c>
@@ -1157,7 +1162,7 @@
       </c>
       <c r="H16" s="1"/>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>45999</v>
       </c>
@@ -1169,7 +1174,7 @@
       </c>
       <c r="H17" s="1"/>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>46006</v>
       </c>
@@ -1181,7 +1186,7 @@
       </c>
       <c r="H18" s="1"/>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>46013</v>
       </c>
@@ -1193,7 +1198,7 @@
       </c>
       <c r="H19" s="1"/>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>46017</v>
       </c>
@@ -1205,7 +1210,7 @@
       </c>
       <c r="H20" s="1"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>46017</v>
       </c>
@@ -1217,7 +1222,7 @@
       </c>
       <c r="H21" s="1"/>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>46020</v>
       </c>
@@ -1229,7 +1234,7 @@
       </c>
       <c r="H22" s="1"/>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>46022</v>
       </c>
@@ -1244,10 +1249,10 @@
       </c>
       <c r="H23" s="1"/>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="H24" s="1"/>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="H25" s="1"/>
     </row>
   </sheetData>
@@ -1258,26 +1263,26 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87863291-4904-4F86-A382-80B6F7D546E9}">
   <dimension ref="A1:E52"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="10.1796875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5" t="s">
+      <c r="C1" s="4"/>
+      <c r="D1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="5"/>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="E1" s="4"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="2"/>
       <c r="B2" s="2" t="s">
         <v>5</v>
@@ -1292,7 +1297,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>45662</v>
       </c>
@@ -1309,7 +1314,7 @@
         <v>895</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>45669</v>
       </c>
@@ -1326,7 +1331,7 @@
         <v>895</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>45676</v>
       </c>
@@ -1343,7 +1348,7 @@
         <v>895</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>45683</v>
       </c>
@@ -1360,7 +1365,7 @@
         <v>895</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>45690</v>
       </c>
@@ -1377,7 +1382,7 @@
         <v>895</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>45697</v>
       </c>
@@ -1394,7 +1399,7 @@
         <v>895</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>45704</v>
       </c>
@@ -1411,7 +1416,7 @@
         <v>915</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>45711</v>
       </c>
@@ -1428,7 +1433,7 @@
         <v>825</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>45718</v>
       </c>
@@ -1445,7 +1450,7 @@
         <v>825</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>45725</v>
       </c>
@@ -1462,7 +1467,7 @@
         <v>825</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>45732</v>
       </c>
@@ -1479,7 +1484,7 @@
         <v>825</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>45739</v>
       </c>
@@ -1496,7 +1501,7 @@
         <v>975</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>45746</v>
       </c>
@@ -1513,7 +1518,7 @@
         <v>975</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>45753</v>
       </c>
@@ -1530,7 +1535,7 @@
         <v>975</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>45760</v>
       </c>
@@ -1547,7 +1552,7 @@
         <v>975</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>45767</v>
       </c>
@@ -1564,7 +1569,7 @@
         <v>975</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>45774</v>
       </c>
@@ -1581,7 +1586,7 @@
         <v>975</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>45781</v>
       </c>
@@ -1598,7 +1603,7 @@
         <v>975</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>45788</v>
       </c>
@@ -1615,7 +1620,7 @@
         <v>975</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>45795</v>
       </c>
@@ -1632,7 +1637,7 @@
         <v>975</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>45802</v>
       </c>
@@ -1649,7 +1654,7 @@
         <v>975</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>45809</v>
       </c>
@@ -1666,7 +1671,7 @@
         <v>975</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>45816</v>
       </c>
@@ -1683,7 +1688,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>45823</v>
       </c>
@@ -1700,7 +1705,7 @@
         <v>975</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>45830</v>
       </c>
@@ -1717,7 +1722,7 @@
         <v>975</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>45837</v>
       </c>
@@ -1734,7 +1739,7 @@
         <v>975</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>45844</v>
       </c>
@@ -1751,7 +1756,7 @@
         <v>975</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>45851</v>
       </c>
@@ -1768,7 +1773,7 @@
         <v>975</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>45858</v>
       </c>
@@ -1785,7 +1790,7 @@
         <v>975</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>45865</v>
       </c>
@@ -1802,9 +1807,9 @@
         <v>975</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A33" s="3">
-        <v>37834</v>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="1">
+        <v>45872</v>
       </c>
       <c r="B33">
         <v>1600</v>
@@ -1819,7 +1824,7 @@
         <v>975</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>45879</v>
       </c>
@@ -1836,7 +1841,7 @@
         <v>975</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>45886</v>
       </c>
@@ -1853,7 +1858,7 @@
         <v>945</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>45893</v>
       </c>
@@ -1870,7 +1875,7 @@
         <v>945</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>45900</v>
       </c>
@@ -1887,7 +1892,7 @@
         <v>945</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>45907</v>
       </c>
@@ -1904,7 +1909,7 @@
         <v>945</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <v>45914</v>
       </c>
@@ -1921,7 +1926,7 @@
         <v>945</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
         <v>45921</v>
       </c>
@@ -1938,7 +1943,7 @@
         <v>945</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>45928</v>
       </c>
@@ -1955,7 +1960,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
         <v>45935</v>
       </c>
@@ -1972,7 +1977,7 @@
         <v>945</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
         <v>45942</v>
       </c>
@@ -1989,7 +1994,7 @@
         <v>945</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <v>45949</v>
       </c>
@@ -2006,7 +2011,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
         <v>45956</v>
       </c>
@@ -2023,7 +2028,7 @@
         <v>945</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
         <v>45963</v>
       </c>
@@ -2040,7 +2045,7 @@
         <v>945</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
         <v>45970</v>
       </c>
@@ -2057,7 +2062,7 @@
         <v>945</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
         <v>45977</v>
       </c>
@@ -2074,7 +2079,7 @@
         <v>945</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
         <v>45984</v>
       </c>
@@ -2091,7 +2096,7 @@
         <v>945</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
         <v>45991</v>
       </c>
@@ -2108,7 +2113,7 @@
         <v>945</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
         <v>45998</v>
       </c>
@@ -2125,7 +2130,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
         <v>46005</v>
       </c>
@@ -2153,13 +2158,13 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B80C934F-57D9-458F-A5EB-DEB9EE8057C9}">
-  <dimension ref="A1:D69"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:D70"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="37.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2173,7 +2178,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>45662</v>
       </c>
@@ -2184,7 +2189,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>45662</v>
       </c>
@@ -2195,7 +2200,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>45669</v>
       </c>
@@ -2206,7 +2211,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>45669</v>
       </c>
@@ -2217,18 +2222,18 @@
         <v>50</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>45669</v>
       </c>
       <c r="B6" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="C6">
         <v>2045</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>45669</v>
       </c>
@@ -2239,7 +2244,7 @@
         <v>2150</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>45676</v>
       </c>
@@ -2250,7 +2255,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>45683</v>
       </c>
@@ -2261,7 +2266,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>45690</v>
       </c>
@@ -2272,7 +2277,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>45690</v>
       </c>
@@ -2283,7 +2288,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>45690</v>
       </c>
@@ -2293,25 +2298,22 @@
       <c r="C12">
         <v>2423</v>
       </c>
-      <c r="D12">
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <v>45690</v>
+      </c>
+      <c r="B13" t="s">
+        <v>25</v>
+      </c>
+      <c r="D13">
         <v>3325</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A13" s="1">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
         <v>45697</v>
       </c>
-      <c r="B13" t="s">
-        <v>21</v>
-      </c>
-      <c r="C13">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A14" s="1">
-        <v>45704</v>
-      </c>
       <c r="B14" t="s">
         <v>21</v>
       </c>
@@ -2319,186 +2321,186 @@
         <v>800</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>45704</v>
       </c>
       <c r="B15" t="s">
+        <v>21</v>
+      </c>
+      <c r="C15">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
+        <v>45704</v>
+      </c>
+      <c r="B16" t="s">
         <v>17</v>
       </c>
-      <c r="C15">
+      <c r="C16">
         <v>50</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A16" s="1">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="1">
         <v>45711</v>
       </c>
-      <c r="B16" t="s">
-        <v>21</v>
-      </c>
-      <c r="C16">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A17" s="1">
+      <c r="B17" t="s">
+        <v>21</v>
+      </c>
+      <c r="C17">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" s="1">
         <v>45718</v>
       </c>
-      <c r="B17" t="s">
-        <v>21</v>
-      </c>
-      <c r="C17">
+      <c r="B18" t="s">
+        <v>21</v>
+      </c>
+      <c r="C18">
         <v>750</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A18" s="1">
-        <v>45725</v>
-      </c>
-      <c r="B18" t="s">
-        <v>21</v>
-      </c>
-      <c r="C18">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>45725</v>
       </c>
       <c r="B19" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="C19">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>45725</v>
       </c>
       <c r="B20" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C20">
-        <v>4045</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>45725</v>
       </c>
       <c r="B21" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="C21">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+        <v>4045</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>45725</v>
       </c>
       <c r="B22" t="s">
+        <v>28</v>
+      </c>
+      <c r="C22">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" s="1">
+        <v>45725</v>
+      </c>
+      <c r="B23" t="s">
         <v>35</v>
       </c>
-      <c r="C22">
+      <c r="C23">
         <v>100</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A23" s="1">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" s="1">
         <v>45732</v>
       </c>
-      <c r="B23" t="s">
-        <v>21</v>
-      </c>
-      <c r="C23">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A24" s="1">
+      <c r="B24" t="s">
+        <v>21</v>
+      </c>
+      <c r="C24">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" s="1">
         <v>45739</v>
       </c>
-      <c r="B24" t="s">
-        <v>21</v>
-      </c>
-      <c r="C24">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A25" s="1">
-        <v>45745</v>
-      </c>
       <c r="B25" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="C25">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>45745</v>
       </c>
       <c r="B26" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C26">
-        <v>1080</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>45745</v>
       </c>
       <c r="B27" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="C27">
-        <v>1100</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+        <v>1080</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>45745</v>
       </c>
       <c r="B28" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C28">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>45745</v>
       </c>
       <c r="B29" t="s">
+        <v>30</v>
+      </c>
+      <c r="C29">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" s="1">
+        <v>45745</v>
+      </c>
+      <c r="B30" t="s">
         <v>32</v>
       </c>
-      <c r="C29">
+      <c r="C30">
         <v>427</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A30" s="1">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" s="1">
         <v>45746</v>
       </c>
-      <c r="B30" t="s">
-        <v>21</v>
-      </c>
-      <c r="C30">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A31" s="1">
-        <v>45753</v>
-      </c>
       <c r="B31" t="s">
         <v>21</v>
       </c>
@@ -2506,219 +2508,219 @@
         <v>800</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>45753</v>
       </c>
       <c r="B32" t="s">
+        <v>21</v>
+      </c>
+      <c r="C32">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" s="1">
+        <v>45753</v>
+      </c>
+      <c r="B33" t="s">
         <v>31</v>
       </c>
-      <c r="C32">
+      <c r="C33">
         <v>200</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A33" s="1">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" s="1">
         <v>45760</v>
       </c>
-      <c r="B33" t="s">
-        <v>21</v>
-      </c>
-      <c r="C33">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A34" s="1">
+      <c r="B34" t="s">
+        <v>21</v>
+      </c>
+      <c r="C34">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" s="1">
         <v>45767</v>
       </c>
-      <c r="B34" t="s">
-        <v>21</v>
-      </c>
-      <c r="C34">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A35" s="1">
+      <c r="B35" t="s">
+        <v>21</v>
+      </c>
+      <c r="C35">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" s="1">
         <v>45774</v>
       </c>
-      <c r="B35" t="s">
-        <v>21</v>
-      </c>
-      <c r="C35">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A36" s="1">
-        <v>45781</v>
-      </c>
       <c r="B36" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="C36">
-        <v>2230</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>45781</v>
       </c>
       <c r="B37" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="C37">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
+        <v>2230</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
+        <v>45781</v>
+      </c>
+      <c r="B38" t="s">
+        <v>21</v>
+      </c>
+      <c r="C38">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" s="1">
         <v>45788</v>
       </c>
-      <c r="B38" t="s">
-        <v>21</v>
-      </c>
-      <c r="C38">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A39" s="1">
+      <c r="B39" t="s">
+        <v>21</v>
+      </c>
+      <c r="C39">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" s="1">
         <v>45795</v>
       </c>
-      <c r="B39" t="s">
-        <v>21</v>
-      </c>
-      <c r="C39">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A40" s="1">
+      <c r="B40" t="s">
+        <v>21</v>
+      </c>
+      <c r="C40">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" s="1">
         <v>45802</v>
       </c>
-      <c r="B40" t="s">
-        <v>21</v>
-      </c>
-      <c r="C40">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A41" s="1">
+      <c r="B41" t="s">
+        <v>21</v>
+      </c>
+      <c r="C41">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" s="1">
         <v>45809</v>
       </c>
-      <c r="B41" t="s">
-        <v>21</v>
-      </c>
-      <c r="C41">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A42" s="1">
+      <c r="B42" t="s">
+        <v>21</v>
+      </c>
+      <c r="C42">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" s="1">
         <v>45816</v>
       </c>
-      <c r="B42" t="s">
-        <v>21</v>
-      </c>
-      <c r="C42">
+      <c r="B43" t="s">
+        <v>21</v>
+      </c>
+      <c r="C43">
         <v>650</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A43" s="1">
-        <v>45823</v>
-      </c>
-      <c r="B43" t="s">
-        <v>21</v>
-      </c>
-      <c r="C43">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <v>45823</v>
       </c>
       <c r="B44" t="s">
+        <v>21</v>
+      </c>
+      <c r="C44">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45" s="1">
+        <v>45823</v>
+      </c>
+      <c r="B45" t="s">
         <v>36</v>
       </c>
-      <c r="C44">
+      <c r="C45">
         <v>150</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A45" s="1">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46" s="1">
         <v>45830</v>
       </c>
-      <c r="B45" t="s">
-        <v>21</v>
-      </c>
-      <c r="C45">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A46" s="1">
+      <c r="B46" t="s">
+        <v>21</v>
+      </c>
+      <c r="C46">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47" s="1">
         <v>45837</v>
       </c>
-      <c r="B46" t="s">
-        <v>21</v>
-      </c>
-      <c r="C46">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A47" s="1">
+      <c r="B47" t="s">
+        <v>21</v>
+      </c>
+      <c r="C47">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48" s="1">
         <v>45844</v>
       </c>
-      <c r="B47" t="s">
-        <v>21</v>
-      </c>
-      <c r="C47">
+      <c r="B48" t="s">
+        <v>21</v>
+      </c>
+      <c r="C48">
         <v>650</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A48" s="1">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49" s="1">
         <v>45851</v>
       </c>
-      <c r="B48" t="s">
-        <v>21</v>
-      </c>
-      <c r="C48">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A49" s="1">
+      <c r="B49" t="s">
+        <v>21</v>
+      </c>
+      <c r="C49">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" s="1">
         <v>45858</v>
       </c>
-      <c r="B49" t="s">
-        <v>21</v>
-      </c>
-      <c r="C49">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A50" s="1">
+      <c r="B50" t="s">
+        <v>21</v>
+      </c>
+      <c r="C50">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" s="1">
         <v>45865</v>
       </c>
-      <c r="B50" t="s">
-        <v>21</v>
-      </c>
-      <c r="C50">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A51" s="3">
-        <v>37834</v>
-      </c>
       <c r="B51" t="s">
         <v>21</v>
       </c>
@@ -2726,201 +2728,212 @@
         <v>800</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
+        <v>45872</v>
+      </c>
+      <c r="B52" t="s">
+        <v>21</v>
+      </c>
+      <c r="C52">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53" s="1">
         <v>45879</v>
       </c>
-      <c r="B52" t="s">
-        <v>21</v>
-      </c>
-      <c r="C52">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A53" s="1">
+      <c r="B53" t="s">
+        <v>21</v>
+      </c>
+      <c r="C53">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54" s="1">
         <v>45886</v>
       </c>
-      <c r="B53" t="s">
-        <v>21</v>
-      </c>
-      <c r="C53">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A54" s="1">
+      <c r="B54" t="s">
+        <v>21</v>
+      </c>
+      <c r="C54">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55" s="1">
         <v>45893</v>
       </c>
-      <c r="B54" t="s">
-        <v>21</v>
-      </c>
-      <c r="C54">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A55" s="1">
+      <c r="B55" t="s">
+        <v>21</v>
+      </c>
+      <c r="C55">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56" s="1">
         <v>45900</v>
       </c>
-      <c r="B55" t="s">
-        <v>21</v>
-      </c>
-      <c r="C55">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A56" s="1">
+      <c r="B56" t="s">
+        <v>21</v>
+      </c>
+      <c r="C56">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57" s="1">
         <v>45907</v>
       </c>
-      <c r="B56" t="s">
-        <v>21</v>
-      </c>
-      <c r="C56">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A57" s="1">
+      <c r="B57" t="s">
+        <v>21</v>
+      </c>
+      <c r="C57">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58" s="1">
         <v>45914</v>
       </c>
-      <c r="B57" t="s">
-        <v>21</v>
-      </c>
-      <c r="C57">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A58" s="1">
+      <c r="B58" t="s">
+        <v>21</v>
+      </c>
+      <c r="C58">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59" s="1">
         <v>45921</v>
       </c>
-      <c r="B58" t="s">
-        <v>21</v>
-      </c>
-      <c r="C58">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A59" s="1">
+      <c r="B59" t="s">
+        <v>21</v>
+      </c>
+      <c r="C59">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60" s="1">
         <v>45935</v>
       </c>
-      <c r="B59" t="s">
-        <v>21</v>
-      </c>
-      <c r="C59">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A60" s="1">
+      <c r="B60" t="s">
+        <v>21</v>
+      </c>
+      <c r="C60">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61" s="1">
         <v>45942</v>
       </c>
-      <c r="B60" t="s">
-        <v>21</v>
-      </c>
-      <c r="C60">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A61" s="1">
-        <v>45956</v>
-      </c>
       <c r="B61" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="C61">
-        <v>2250</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.35">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
         <v>45956</v>
       </c>
       <c r="B62" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="C62">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.35">
+        <v>2250</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
+        <v>45956</v>
+      </c>
+      <c r="B63" t="s">
+        <v>21</v>
+      </c>
+      <c r="C63">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64" s="1">
         <v>45963</v>
       </c>
-      <c r="B63" t="s">
-        <v>21</v>
-      </c>
-      <c r="C63">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A64" s="1">
+      <c r="B64" t="s">
+        <v>21</v>
+      </c>
+      <c r="C64">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" s="1">
         <v>45970</v>
       </c>
-      <c r="B64" t="s">
-        <v>21</v>
-      </c>
-      <c r="C64">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A65" s="1">
+      <c r="B65" t="s">
+        <v>21</v>
+      </c>
+      <c r="C65">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66" s="1">
         <v>45977</v>
       </c>
-      <c r="B65" t="s">
-        <v>21</v>
-      </c>
-      <c r="C65">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A66" s="1">
+      <c r="B66" t="s">
+        <v>21</v>
+      </c>
+      <c r="C66">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67" s="1">
         <v>45984</v>
       </c>
-      <c r="B66" t="s">
-        <v>21</v>
-      </c>
-      <c r="C66">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A67" s="1">
+      <c r="B67" t="s">
+        <v>21</v>
+      </c>
+      <c r="C67">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68" s="1">
         <v>45991</v>
       </c>
-      <c r="B67" t="s">
-        <v>21</v>
-      </c>
-      <c r="C67">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A68" s="1">
+      <c r="B68" t="s">
+        <v>21</v>
+      </c>
+      <c r="C68">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A69" s="1">
         <v>45998</v>
       </c>
-      <c r="B68" t="s">
-        <v>21</v>
-      </c>
-      <c r="C68">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A69" s="1">
+      <c r="B69" t="s">
+        <v>21</v>
+      </c>
+      <c r="C69">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A70" s="1">
         <v>46005</v>
       </c>
-      <c r="B69" t="s">
-        <v>21</v>
-      </c>
-      <c r="C69">
+      <c r="B70" t="s">
+        <v>21</v>
+      </c>
+      <c r="C70">
         <v>800</v>
       </c>
     </row>
